--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:43</t>
+    <t xml:space="preserve">2026-09-09 22:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:30</t>
+    <t xml:space="preserve">2026-09-12 19:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_maule.xlsx
@@ -36,100 +36,100 @@
     <t xml:space="preserve">Maule</t>
   </si>
   <si>
+    <t xml:space="preserve">Yerbas Buenas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parral</t>
+  </si>
+  <si>
     <t xml:space="preserve">Longaví</t>
   </si>
   <si>
-    <t xml:space="preserve">Parral</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Clemente</t>
   </si>
   <si>
-    <t xml:space="preserve">Yerbas Buenas</t>
+    <t xml:space="preserve">San Javier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelarco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cauquenes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Rafael</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romeral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pelluhue</t>
   </si>
   <si>
     <t xml:space="preserve">Colbún</t>
   </si>
   <si>
-    <t xml:space="preserve">San Javier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelluhue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pelarco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linares</t>
+    <t xml:space="preserve">Hualañé</t>
   </si>
   <si>
     <t xml:space="preserve">Retiro</t>
   </si>
   <si>
-    <t xml:space="preserve">Romeral</t>
+    <t xml:space="preserve">Sagrada Familia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Claro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pencahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa Alegre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constitución</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licantén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rauco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vichuquén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curepto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chanco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empedrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curicó</t>
   </si>
   <si>
     <t xml:space="preserve">Talca</t>
   </si>
   <si>
-    <t xml:space="preserve">Río Claro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villa Alegre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Rafael</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualañé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cauquenes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sagrada Familia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curepto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rauco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vichuquén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licantén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pencahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Constitución</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empedrado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curicó</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:46</t>
+    <t xml:space="preserve">2026-09-24 00:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -556,13 +556,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>7403</v>
+        <v>7408</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5382</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="3">
@@ -570,16 +570,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7105</v>
+        <v>7401</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4259</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="4">
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>7404</v>
@@ -596,7 +596,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2905</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="5">
@@ -604,16 +604,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>7109</v>
+        <v>7403</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2709</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="6">
@@ -621,16 +621,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>7408</v>
+        <v>7109</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2430</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -638,16 +638,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7402</v>
+        <v>7105</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2188</v>
+        <v>928</v>
       </c>
     </row>
     <row r="8">
@@ -664,7 +664,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2174</v>
+        <v>866</v>
       </c>
     </row>
     <row r="9">
@@ -675,13 +675,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>7203</v>
+        <v>7304</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1723</v>
+        <v>808</v>
       </c>
     </row>
     <row r="10">
@@ -698,7 +698,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1594</v>
+        <v>671</v>
       </c>
     </row>
     <row r="11">
@@ -709,13 +709,13 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>7401</v>
+        <v>7201</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1572</v>
+        <v>647</v>
       </c>
     </row>
     <row r="12">
@@ -726,13 +726,13 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>7405</v>
+        <v>7110</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1432</v>
+        <v>619</v>
       </c>
     </row>
     <row r="13">
@@ -749,7 +749,7 @@
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1331</v>
+        <v>575</v>
       </c>
     </row>
     <row r="14">
@@ -760,13 +760,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>7101</v>
+        <v>7203</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1314</v>
+        <v>529</v>
       </c>
     </row>
     <row r="15">
@@ -777,13 +777,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>7108</v>
+        <v>7402</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1309</v>
+        <v>473</v>
       </c>
     </row>
     <row r="16">
@@ -794,13 +794,13 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>7304</v>
+        <v>7302</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1194</v>
+        <v>341</v>
       </c>
     </row>
     <row r="17">
@@ -811,13 +811,13 @@
         <v>20</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>7407</v>
+        <v>7405</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1168</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18">
@@ -828,13 +828,13 @@
         <v>21</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>7110</v>
+        <v>7307</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>926</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19">
@@ -845,13 +845,13 @@
         <v>22</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>7302</v>
+        <v>7108</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>921</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20">
@@ -868,7 +868,7 @@
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>850</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21">
@@ -879,13 +879,13 @@
         <v>24</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>7201</v>
+        <v>7107</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>837</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22">
@@ -896,13 +896,13 @@
         <v>25</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>7307</v>
+        <v>7407</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>717</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23">
@@ -913,13 +913,13 @@
         <v>26</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>7103</v>
+        <v>7102</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>556</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24">
@@ -930,13 +930,13 @@
         <v>27</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>7305</v>
+        <v>7303</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>347</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25">
@@ -947,13 +947,13 @@
         <v>28</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>7309</v>
+        <v>7305</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>310</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26">
@@ -964,13 +964,13 @@
         <v>29</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>7303</v>
+        <v>7309</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>293</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -981,13 +981,13 @@
         <v>30</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>7107</v>
+        <v>7103</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>242</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="28">
@@ -1004,7 +1004,7 @@
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>159</v>
+        <v>-29</v>
       </c>
     </row>
     <row r="29">
@@ -1015,13 +1015,13 @@
         <v>32</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>7102</v>
+        <v>7104</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-18</v>
+        <v>-107</v>
       </c>
     </row>
     <row r="30">
@@ -1032,13 +1032,13 @@
         <v>33</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>7104</v>
+        <v>7301</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-143</v>
+        <v>-318</v>
       </c>
     </row>
     <row r="31">
@@ -1049,13 +1049,13 @@
         <v>34</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>7301</v>
+        <v>7101</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-637</v>
+        <v>-453</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:24</t>
+    <t xml:space="preserve">2026-09-27 22:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:13</t>
+    <t xml:space="preserve">2026-10-01 20:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:54</t>
+    <t xml:space="preserve">2026-10-02 13:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:18</t>
+    <t xml:space="preserve">2026-10-05 08:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
